--- a/Design-Files/Power-PCB-v1.0/Deliverables/BOM/Client-BOM_Power-PCB-v1.0.xlsx
+++ b/Design-Files/Power-PCB-v1.0/Deliverables/BOM/Client-BOM_Power-PCB-v1.0.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-consultants\dustinm-lampleddriver\Design-Files\Power-PCB-v1.0\Deliverables\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\dustinm-lampleddriver\Design-Files\Power-PCB-v1.0\Deliverables\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -1355,21 +1355,21 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="A1:K59"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="3.109375" style="4" customWidth="1"/>
-    <col min="3" max="3" width="18.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.140625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="18.7109375" style="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="36" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="33.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="29.44140625" customWidth="1"/>
+    <col min="6" max="6" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="29.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -1382,7 +1382,7 @@
       <c r="J1" s="14"/>
       <c r="K1" s="14"/>
     </row>
-    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="5" t="s">
         <v>0</v>
@@ -1415,7 +1415,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="11">
         <f>ROW(B3) - ROW($B$2)</f>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="K3" s="7"/>
     </row>
-    <row r="4" spans="1:11" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="11">
         <f t="shared" ref="B4:B58" si="0">ROW(B4) - ROW($B$2)</f>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="K4" s="9"/>
     </row>
-    <row r="5" spans="1:11" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="11">
         <f>ROW(B5) - ROW($B$2)</f>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="K5" s="7"/>
     </row>
-    <row r="6" spans="1:11" ht="48.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="11">
         <f t="shared" si="0"/>
@@ -1543,7 +1543,7 @@
       </c>
       <c r="K6" s="9"/>
     </row>
-    <row r="7" spans="1:11" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="11">
         <f>ROW(B7) - ROW($B$2)</f>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="K7" s="7"/>
     </row>
-    <row r="8" spans="1:11" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="11">
         <f t="shared" si="0"/>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="K8" s="9"/>
     </row>
-    <row r="9" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="11">
         <f>ROW(B9) - ROW($B$2)</f>
@@ -1639,7 +1639,7 @@
       </c>
       <c r="K9" s="7"/>
     </row>
-    <row r="10" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="11">
         <f t="shared" si="0"/>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="K10" s="9"/>
     </row>
-    <row r="11" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="11">
         <f>ROW(B11) - ROW($B$2)</f>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="K11" s="7"/>
     </row>
-    <row r="12" spans="1:11" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="11">
         <f t="shared" si="0"/>
@@ -1731,7 +1731,7 @@
       </c>
       <c r="K12" s="9"/>
     </row>
-    <row r="13" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="11">
         <f>ROW(B13) - ROW($B$2)</f>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="K13" s="7"/>
     </row>
-    <row r="14" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="11">
         <f t="shared" si="0"/>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="K14" s="9"/>
     </row>
-    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="11">
         <f>ROW(B15) - ROW($B$2)</f>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="K15" s="7"/>
     </row>
-    <row r="16" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1"/>
       <c r="B16" s="11">
         <f t="shared" si="0"/>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="K16" s="9"/>
     </row>
-    <row r="17" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1"/>
       <c r="B17" s="11">
         <f>ROW(B17) - ROW($B$2)</f>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="K17" s="7"/>
     </row>
-    <row r="18" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1"/>
       <c r="B18" s="11">
         <f t="shared" si="0"/>
@@ -1919,7 +1919,7 @@
       </c>
       <c r="K18" s="9"/>
     </row>
-    <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1"/>
       <c r="B19" s="11">
         <f>ROW(B19) - ROW($B$2)</f>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="K19" s="7"/>
     </row>
-    <row r="20" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1"/>
       <c r="B20" s="11">
         <f t="shared" si="0"/>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="K20" s="9"/>
     </row>
-    <row r="21" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="11">
         <f>ROW(B21) - ROW($B$2)</f>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="K21" s="7"/>
     </row>
-    <row r="22" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
       <c r="B22" s="11">
         <f t="shared" si="0"/>
@@ -2047,7 +2047,7 @@
       </c>
       <c r="K22" s="9"/>
     </row>
-    <row r="23" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
       <c r="B23" s="11">
         <f>ROW(B23) - ROW($B$2)</f>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="K23" s="7"/>
     </row>
-    <row r="24" spans="1:11" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="B24" s="11">
         <f t="shared" si="0"/>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="K24" s="9"/>
     </row>
-    <row r="25" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
       <c r="B25" s="11">
         <f>ROW(B25) - ROW($B$2)</f>
@@ -2143,7 +2143,7 @@
       </c>
       <c r="K25" s="7"/>
     </row>
-    <row r="26" spans="1:11" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
       <c r="B26" s="11">
         <f t="shared" si="0"/>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="K26" s="9"/>
     </row>
-    <row r="27" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="B27" s="11">
         <f>ROW(B27) - ROW($B$2)</f>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="K27" s="7"/>
     </row>
-    <row r="28" spans="1:11" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:11" ht="48.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
       <c r="B28" s="11">
         <f t="shared" si="0"/>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="K28" s="9"/>
     </row>
-    <row r="29" spans="1:11" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
       <c r="B29" s="11">
         <f>ROW(B29) - ROW($B$2)</f>
@@ -2271,7 +2271,7 @@
       </c>
       <c r="K29" s="7"/>
     </row>
-    <row r="30" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
       <c r="B30" s="11">
         <f t="shared" si="0"/>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="K30" s="9"/>
     </row>
-    <row r="31" spans="1:11" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
       <c r="B31" s="11">
         <f>ROW(B31) - ROW($B$2)</f>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="K31" s="7"/>
     </row>
-    <row r="32" spans="1:11" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="B32" s="11">
         <f t="shared" si="0"/>
@@ -2367,7 +2367,7 @@
       </c>
       <c r="K32" s="9"/>
     </row>
-    <row r="33" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="B33" s="11">
         <f>ROW(B33) - ROW($B$2)</f>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="K33" s="7"/>
     </row>
-    <row r="34" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="11">
         <f t="shared" si="0"/>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="K34" s="9"/>
     </row>
-    <row r="35" spans="1:11" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" ht="24.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="1"/>
       <c r="B35" s="11">
         <f>ROW(B35) - ROW($B$2)</f>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K35" s="7"/>
     </row>
-    <row r="36" spans="1:11" ht="24.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1"/>
       <c r="B36" s="11">
         <f t="shared" si="0"/>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="K36" s="9"/>
     </row>
-    <row r="37" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="1"/>
       <c r="B37" s="11">
         <f>ROW(B37) - ROW($B$2)</f>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="K37" s="7"/>
     </row>
-    <row r="38" spans="1:11" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1"/>
       <c r="B38" s="11">
         <f t="shared" si="0"/>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="K38" s="9"/>
     </row>
-    <row r="39" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="1"/>
       <c r="B39" s="11">
         <f>ROW(B39) - ROW($B$2)</f>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="K39" s="7"/>
     </row>
-    <row r="40" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1"/>
       <c r="B40" s="11">
         <f t="shared" si="0"/>
@@ -2623,7 +2623,7 @@
       </c>
       <c r="K40" s="9"/>
     </row>
-    <row r="41" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1"/>
       <c r="B41" s="11">
         <f>ROW(B41) - ROW($B$2)</f>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="K41" s="7"/>
     </row>
-    <row r="42" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1"/>
       <c r="B42" s="11">
         <f t="shared" si="0"/>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="K42" s="9"/>
     </row>
-    <row r="43" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1"/>
       <c r="B43" s="11">
         <f>ROW(B43) - ROW($B$2)</f>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="K43" s="7"/>
     </row>
-    <row r="44" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1"/>
       <c r="B44" s="11">
         <f t="shared" si="0"/>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="K44" s="9"/>
     </row>
-    <row r="45" spans="1:11" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1"/>
       <c r="B45" s="11">
         <f>ROW(B45) - ROW($B$2)</f>
@@ -2783,7 +2783,7 @@
       </c>
       <c r="K45" s="7"/>
     </row>
-    <row r="46" spans="1:11" ht="36.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:11" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1"/>
       <c r="B46" s="11">
         <f t="shared" si="0"/>
@@ -2815,7 +2815,7 @@
       </c>
       <c r="K46" s="9"/>
     </row>
-    <row r="47" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1"/>
       <c r="B47" s="11">
         <f>ROW(B47) - ROW($B$2)</f>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="K47" s="7"/>
     </row>
-    <row r="48" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1"/>
       <c r="B48" s="11">
         <f t="shared" si="0"/>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="K48" s="9"/>
     </row>
-    <row r="49" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1"/>
       <c r="B49" s="11">
         <f>ROW(B49) - ROW($B$2)</f>
@@ -2911,7 +2911,7 @@
       </c>
       <c r="K49" s="7"/>
     </row>
-    <row r="50" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1"/>
       <c r="B50" s="11">
         <f t="shared" si="0"/>
@@ -2943,7 +2943,7 @@
       </c>
       <c r="K50" s="9"/>
     </row>
-    <row r="51" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1"/>
       <c r="B51" s="11">
         <f>ROW(B51) - ROW($B$2)</f>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="K51" s="7"/>
     </row>
-    <row r="52" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1"/>
       <c r="B52" s="11">
         <f t="shared" si="0"/>
@@ -3007,7 +3007,7 @@
       </c>
       <c r="K52" s="9"/>
     </row>
-    <row r="53" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1"/>
       <c r="B53" s="11">
         <f>ROW(B53) - ROW($B$2)</f>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="K53" s="7"/>
     </row>
-    <row r="54" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="11">
         <f t="shared" si="0"/>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="K54" s="9"/>
     </row>
-    <row r="55" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1"/>
       <c r="B55" s="11">
         <f>ROW(B55) - ROW($B$2)</f>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="K55" s="7"/>
     </row>
-    <row r="56" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="11">
         <f t="shared" si="0"/>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="K56" s="9"/>
     </row>
-    <row r="57" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1"/>
       <c r="B57" s="11">
         <f>ROW(B57) - ROW($B$2)</f>
@@ -3167,7 +3167,7 @@
       </c>
       <c r="K57" s="7"/>
     </row>
-    <row r="58" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1"/>
       <c r="B58" s="11">
         <f t="shared" si="0"/>
@@ -3199,7 +3199,7 @@
       </c>
       <c r="K58" s="9"/>
     </row>
-    <row r="59" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1"/>
       <c r="B59" s="11">
         <f>ROW(B59) - ROW($B$2)</f>
